--- a/docs/reports/连通标注_2026-07-04_分表/5_市场.xlsx
+++ b/docs/reports/连通标注_2026-07-04_分表/5_市场.xlsx
@@ -1456,14 +1456,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K3" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K3" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>无 Caplight API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (企业订阅,询价)</t>
         </is>
       </c>
     </row>
@@ -1514,14 +1514,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K4" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K4" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>无 Forge Global API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 403),返回需鉴权;注册表:付费</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="K5" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -1630,14 +1630,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K6" s="185" t="inlineStr">
-        <is>
-          <t>➖ 方式未支持</t>
+      <c r="K6" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>'SEC EDGAR + 新闻流' 无匹配 fetcher</t>
+          <t>验证:接口/官网可达(HTTP 403),返回需鉴权;经API取数</t>
         </is>
       </c>
     </row>
@@ -1688,14 +1688,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K7" s="185" t="inlineStr">
-        <is>
-          <t>➖ 方式未支持</t>
+      <c r="K7" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>'—(暂不启用)' 无匹配 fetcher</t>
+          <t>验证:接口/官网可达(HTTP 403),返回需鉴权;注册表:付费</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="K8" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1804,14 +1804,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K9" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K9" s="184" t="inlineStr">
+        <is>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>无 IT桔子 API provider 插件</t>
+          <t>验证:HTTP 412</t>
         </is>
       </c>
     </row>
@@ -1862,14 +1862,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K10" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K10" s="184" t="inlineStr">
+        <is>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>无 鲸准 Rhino API provider 插件</t>
+          <t xml:space="preserve">验证:ERR ConnectError: [SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in </t>
         </is>
       </c>
     </row>
@@ -1920,14 +1920,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K11" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K11" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>无 投中 CVSource API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="K12" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="K13" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2094,14 +2094,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K14" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K14" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>无 AKShare API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -2152,14 +2152,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K15" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K15" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>无 AKShare API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="K16" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="K17" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="K18" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -2386,12 +2386,12 @@
       </c>
       <c r="K19" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="K20" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -2502,12 +2502,12 @@
       </c>
       <c r="K21" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="K22" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -2618,12 +2618,12 @@
       </c>
       <c r="K23" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="K24" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -2734,12 +2734,12 @@
       </c>
       <c r="K25" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="K26" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -2848,14 +2848,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K27" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K27" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>无 AKShare API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -2906,14 +2906,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K28" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K28" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>无 AKShare API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -2966,12 +2966,12 @@
       </c>
       <c r="K29" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -3022,14 +3022,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K30" s="185" t="inlineStr">
-        <is>
-          <t>➖ 方式未支持</t>
+      <c r="K30" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>'FINRA 公开' 无匹配 fetcher</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -3082,12 +3082,12 @@
       </c>
       <c r="K31" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API + FINRA)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -3138,14 +3138,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K32" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K32" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>无 TreasuryDirect API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -3196,14 +3196,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K33" s="183" t="inlineStr">
-        <is>
-          <t>🔑 需API密钥</t>
+      <c r="K33" s="184" t="inlineStr">
+        <is>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FRED API)</t>
+          <t xml:space="preserve">验证:ERR ConnectError: [SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in </t>
         </is>
       </c>
     </row>
@@ -3254,14 +3254,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K34" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K34" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>无 AKShare API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -3312,14 +3312,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K35" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K35" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>无 AKShare API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -3370,14 +3370,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K36" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K36" s="184" t="inlineStr">
+        <is>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>无 USDA API provider 插件</t>
+          <t>验证:ERR ReadTimeout: The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -3430,12 +3430,12 @@
       </c>
       <c r="K37" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -3488,12 +3488,12 @@
       </c>
       <c r="K38" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K39" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K39" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>无 EIA API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -3604,12 +3604,12 @@
       </c>
       <c r="K40" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>HTTP 403,反爬/拒绝访问</t>
+          <t>HTTP 403,访问被拒</t>
         </is>
       </c>
     </row>
@@ -3660,14 +3660,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K41" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K41" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·部分需付费</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>无 GIE AGSI+ API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:免费/部分付费</t>
         </is>
       </c>
     </row>
@@ -3720,12 +3720,12 @@
       </c>
       <c r="K42" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -3778,12 +3778,12 @@
       </c>
       <c r="K43" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -3836,12 +3836,12 @@
       </c>
       <c r="K44" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -3892,14 +3892,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K45" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K45" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>无 ECB API (CSV) provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -3950,14 +3950,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K46" s="185" t="inlineStr">
-        <is>
-          <t>➖ 方式未支持</t>
+      <c r="K46" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>'Fed H.10' 无匹配 fetcher</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -4010,12 +4010,12 @@
       </c>
       <c r="K47" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -4066,14 +4066,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K48" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K48" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>无 AKShare API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="K49" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -4182,14 +4182,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K50" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K50" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>无 DefiLlama API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -4240,14 +4240,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K51" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K51" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>无 Binance API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -4298,14 +4298,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K52" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K52" s="184" t="inlineStr">
+        <is>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>无 Coinbase API provider 插件</t>
+          <t xml:space="preserve">验证:ERR ConnectError: [SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in </t>
         </is>
       </c>
     </row>
@@ -4356,14 +4356,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K53" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K53" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>无 CoinGecko API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -4416,12 +4416,12 @@
       </c>
       <c r="K54" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FMP API + CoinGecko)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费 (FMP Ultimate≈$99/月)</t>
         </is>
       </c>
     </row>
@@ -4472,14 +4472,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K55" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K55" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>无 Glassnode API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 403),返回需鉴权;注册表:付费</t>
         </is>
       </c>
     </row>
@@ -4530,14 +4530,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K56" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K56" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>无 Nansen API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费</t>
         </is>
       </c>
     </row>
@@ -4588,14 +4588,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K57" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K57" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·部分需付费</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>无 Dune API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:部分付费</t>
         </is>
       </c>
     </row>
@@ -4646,14 +4646,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K58" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K58" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>无 Polymarket API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -4704,14 +4704,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K59" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K59" s="184" t="inlineStr">
+        <is>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>无 Kalshi API provider 插件</t>
+          <t>验证:HTTP 429</t>
         </is>
       </c>
     </row>
@@ -4762,14 +4762,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K60" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K60" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>无 Manifold API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -4820,14 +4820,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K61" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K61" s="184" t="inlineStr">
+        <is>
+          <t>❌ 链接失效</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>无 PredictIt API provider 插件</t>
+          <t>验证:HTTP 404</t>
         </is>
       </c>
     </row>
